--- a/NBFC-MF/Borrowers/Lanchenbi_Ibeyaima_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Lanchenbi_Ibeyaima_Weekly.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="5" r:id="rId1"/>
@@ -1524,31 +1524,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="19">
+        <v>46286</v>
+      </c>
+      <c r="B5" s="23">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>169.86279204898605</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="4"/>
+        <v>530.13720795101392</v>
+      </c>
+      <c r="G5" s="21">
+        <f t="shared" si="5"/>
+        <v>7941.1625030625555</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>2058.8374969374445</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -1785,7 +1787,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1820,7 +1822,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>9800</v>
+        <v>9100</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1855,7 +1857,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8471.2997110135693</v>
+        <v>7941.1625030625555</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1890,7 +1892,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1528.7002889864307</v>
+        <v>2058.8374969374445</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2085,31 +2087,33 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="23" t="str">
+      <c r="A3" s="19">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="23">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="21" t="str">
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E3" s="21">
         <f t="shared" ref="E3:E18" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="21" t="str">
+        <v>571.50053627132684</v>
+      </c>
+      <c r="F3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="21" t="str">
+        <v>1528.4994637286732</v>
+      </c>
+      <c r="G3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21" t="str">
+        <v>26973.047398654715</v>
+      </c>
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H18" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
-        <v/>
+        <v>3026.9526013452851</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>10</v>
@@ -2412,7 +2416,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2447,7 +2451,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>33600</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2482,7 +2486,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>28501.546862383388</v>
+        <v>26973.047398654715</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2517,7 +2521,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1498.4531376166124</v>
+        <v>3026.9526013452851</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Lanchenbi_Ibeyaima_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Lanchenbi_Ibeyaima_Weekly.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="5" r:id="rId1"/>
@@ -1558,31 +1558,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B6" s="22">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>159.23271291313185</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="4"/>
+        <v>540.76728708686812</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="5"/>
+        <v>7400.3952159756873</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>2599.6047840243127</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -1787,7 +1789,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1822,7 +1824,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>9100</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1857,7 +1859,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>7941.1625030625555</v>
+        <v>7400.3952159756873</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1892,7 +1894,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2058.8374969374445</v>
+        <v>2599.6047840243127</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2123,31 +2125,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46290</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>540.8517343859711</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>1559.1482656140288</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>25413.899133040686</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>4586.1008669593139</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -2416,7 +2420,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>31500</v>
+        <v>29400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2486,7 +2490,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>26973.047398654715</v>
+        <v>25413.899133040686</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2521,7 +2525,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3026.9526013452851</v>
+        <v>4586.1008669593139</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Lanchenbi_Ibeyaima_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Lanchenbi_Ibeyaima_Weekly.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Loan1" sheetId="5" r:id="rId1"/>
@@ -1592,31 +1592,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46305</v>
+      </c>
+      <c r="B7" s="23">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>148.38948408557562</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="4"/>
+        <v>551.61051591442435</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="5"/>
+        <v>6848.7847000612628</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>3151.2152999387372</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1626,31 +1628,33 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B8" s="22">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>137.328831582042</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="4"/>
+        <v>562.67116841795803</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="5"/>
+        <v>6286.1135316433047</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>3713.8864683566953</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1789,7 +1793,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1824,7 +1828,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>8400</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1859,7 +1863,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>7400.3952159756873</v>
+        <v>6286.1135316433047</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1894,7 +1898,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2599.6047840243127</v>
+        <v>3713.8864683566953</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2159,31 +2163,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="19">
+        <v>46301</v>
+      </c>
+      <c r="B5" s="23">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>509.58837614695045</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="4"/>
+        <v>1590.4116238530496</v>
+      </c>
+      <c r="G5" s="21">
+        <f t="shared" si="5"/>
+        <v>23823.487509187638</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>6176.5124908123616</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -2191,31 +2197,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B6" s="22">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>477.69813873938818</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="4"/>
+        <v>1622.3018612606118</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="5"/>
+        <v>22201.185647927028</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>7798.8143520729718</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -2420,7 +2428,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2455,7 +2463,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>29400</v>
+        <v>25200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2490,7 +2498,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>25413.899133040686</v>
+        <v>22201.185647927028</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2525,7 +2533,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4586.1008669593139</v>
+        <v>7798.8143520729718</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
